--- a/www/ig/fhir/core/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="134">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-19T12:11:47+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -84,7 +84,9 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This French extension allows to associate the type of service with the duration of this service | Cette extension française permet d'associer le type de service avec la durée de ce service.</t>
+    <t>Cette extension française permet d'associer le type de service avec la durée de ce service.
++This French extension allows to associate the type of service with the duration of this service</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +116,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Extension|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -383,7 +385,10 @@
     <t>example</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type</t>
+    <t>This value set defines an example set of codes of service-types.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/service-type|4.0.1</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -759,42 +764,42 @@
   <dimension ref="A1:AK16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="39.3515625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="28.33203125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.48046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="8.171875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="33.9453125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="24.44140625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="9.90234375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="14.21484375" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="12.26171875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="19.80078125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="38.23046875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="17.4453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="50.078125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="37.5703125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="15.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="22.6796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="19.5625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1698,9 +1703,11 @@
       <c r="X9" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="Y9" s="2"/>
+      <c r="Y9" t="s" s="2">
+        <v>120</v>
+      </c>
       <c r="Z9" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AA9" t="s" s="2">
         <v>79</v>
@@ -1718,7 +1725,7 @@
         <v>79</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1730,7 +1737,7 @@
         <v>79</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>113</v>
@@ -1738,13 +1745,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>92</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>79</v>
@@ -1769,10 +1776,10 @@
         <v>93</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1843,7 +1850,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>103</v>
@@ -1946,7 +1953,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>105</v>
@@ -2049,7 +2056,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>107</v>
@@ -2092,7 +2099,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>79</v>
@@ -2154,7 +2161,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>115</v>
@@ -2180,7 +2187,7 @@
         <v>79</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>117</v>
@@ -2237,7 +2244,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -2249,7 +2256,7 @@
         <v>79</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>113</v>
@@ -2362,10 +2369,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2388,7 +2395,7 @@
         <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>117</v>
@@ -2445,7 +2452,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2457,7 +2464,7 @@
         <v>79</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>113</v>

--- a/www/ig/fhir/core/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="133">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T12:11:47+01:00</t>
+    <t>2024-09-04T10:06:33+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(Work))</t>
+    <t>Interop'Santé (http://interopsante.org/)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -84,9 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Cette extension française permet d'associer le type de service avec la durée de ce service.
--This French extension allows to associate the type of service with the duration of this service</t>
+    <t>This French extension allows to associate the type of service with the duration of this service | Cette extension française permet d'associer le type de service avec la durée de ce service.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -116,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Extension|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -385,10 +383,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>This value set defines an example set of codes of service-types.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/service-type</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -764,42 +759,42 @@
   <dimension ref="A1:AK16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="33.9453125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="24.44140625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="9.90234375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="7.046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="39.3515625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="28.33203125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.48046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="8.171875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="12.26171875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="14.21484375" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="50.078125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="37.5703125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="15.046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="19.80078125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="38.23046875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="17.4453125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="19.5625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="22.6796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1703,29 +1698,27 @@
       <c r="X9" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="Y9" t="s" s="2">
+      <c r="Y9" s="2"/>
+      <c r="Z9" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="Z9" t="s" s="2">
+      <c r="AA9" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>122</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1737,7 +1730,7 @@
         <v>79</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>113</v>
@@ -1745,13 +1738,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>92</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>79</v>
@@ -1776,10 +1769,10 @@
         <v>93</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>127</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1850,7 +1843,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>103</v>
@@ -1953,7 +1946,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>105</v>
@@ -2056,7 +2049,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>107</v>
@@ -2099,7 +2092,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>79</v>
@@ -2161,7 +2154,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>115</v>
@@ -2187,7 +2180,7 @@
         <v>79</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>117</v>
@@ -2244,7 +2237,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -2256,7 +2249,7 @@
         <v>79</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>113</v>
@@ -2369,10 +2362,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2395,7 +2388,7 @@
         <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>117</v>
@@ -2452,7 +2445,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2464,7 +2457,7 @@
         <v>79</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>113</v>

--- a/www/ig/fhir/core/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="134">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-25T18:08:32+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -84,7 +84,9 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This French extension allows to associate the type of service with the duration of this service | Cette extension française permet d'associer le type de service avec la durée de ce service.</t>
+    <t>Cette extension française permet d'associer le type de service avec la durée de ce service.
++This French extension allows to associate the type of service with the duration of this service</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +116,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Extension|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -383,7 +385,10 @@
     <t>example</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type</t>
+    <t>This value set defines an example set of codes of service-types.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/service-type|4.0.1</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -759,42 +764,42 @@
   <dimension ref="A1:AK16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="39.3515625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="28.33203125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.48046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="8.171875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="33.9453125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="24.44140625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="9.90234375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="14.21484375" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="12.26171875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="19.80078125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="38.23046875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="17.4453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="50.078125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="37.5703125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="15.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="22.6796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="19.5625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1698,9 +1703,11 @@
       <c r="X9" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="Y9" s="2"/>
+      <c r="Y9" t="s" s="2">
+        <v>120</v>
+      </c>
       <c r="Z9" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AA9" t="s" s="2">
         <v>79</v>
@@ -1718,7 +1725,7 @@
         <v>79</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1730,7 +1737,7 @@
         <v>79</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>113</v>
@@ -1738,13 +1745,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>92</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>79</v>
@@ -1769,10 +1776,10 @@
         <v>93</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1843,7 +1850,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>103</v>
@@ -1946,7 +1953,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>105</v>
@@ -2049,7 +2056,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>107</v>
@@ -2092,7 +2099,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>79</v>
@@ -2154,7 +2161,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>115</v>
@@ -2180,7 +2187,7 @@
         <v>79</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>117</v>
@@ -2237,7 +2244,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -2249,7 +2256,7 @@
         <v>79</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>113</v>
@@ -2362,10 +2369,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2388,7 +2395,7 @@
         <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>117</v>
@@ -2445,7 +2452,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2457,7 +2464,7 @@
         <v>79</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>113</v>
